--- a/data/a_Eingangsdaten/Testdaten/Test2/testreihe-Bedarf-fluktual_passend_fluktual1_Strom_1Tag.xlsx
+++ b/data/a_Eingangsdaten/Testdaten/Test2/testreihe-Bedarf-fluktual_passend_fluktual1_Strom_1Tag.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HansisRasanterRaser\Desktop\UNI\000_DA\git\knEBiD\data\a_Eingangsdaten\Testdaten\Test2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{107CF18C-BB9A-4CAC-93F3-911A1E15B93D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF5A2B3F-2709-4752-9D5F-EA428F684B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28800" yWindow="2730" windowWidth="28800" windowHeight="11025" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
     <t>Mobilität</t>
   </si>
   <si>
-    <t>Strom [MW]</t>
+    <t>Strom_Gesamt_Bedarf [MW]</t>
   </si>
 </sst>
 </file>
